--- a/excel_files/7.1.1.xlsx
+++ b/excel_files/7.1.1.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\korozbaeva\Desktop\Показатели ЦУР для Платформы\Глобальные показатели ЦУР\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\Показатели ЦУР для Платформы\Глобальные показатели ЦУР — 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14175" windowHeight="8070"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -926,7 +926,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K49"/>
+  <dimension ref="A1:L49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="37.140625" style="1" customWidth="1"/>
@@ -934,7 +934,7 @@
     <col min="8" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>19</v>
       </c>
@@ -953,7 +953,7 @@
       <c r="J1" s="5"/>
       <c r="K1" s="5"/>
     </row>
-    <row r="2" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="35" t="s">
         <v>104</v>
       </c>
@@ -972,7 +972,7 @@
       <c r="J2" s="5"/>
       <c r="K2" s="5"/>
     </row>
-    <row r="3" spans="1:11" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="14"/>
       <c r="B3" s="15"/>
       <c r="C3" s="15"/>
@@ -984,8 +984,9 @@
       <c r="I3" s="36"/>
       <c r="J3" s="36"/>
       <c r="K3" s="36"/>
-    </row>
-    <row r="4" spans="1:11" s="4" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="L3" s="16"/>
+    </row>
+    <row r="4" spans="1:12" s="4" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>20</v>
       </c>
@@ -1019,8 +1020,11 @@
       <c r="K4" s="17">
         <v>2023</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L4" s="17">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="18" t="s">
         <v>52</v>
       </c>
@@ -1054,8 +1058,11 @@
       <c r="K5" s="37">
         <v>73.212978783392558</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L5" s="37">
+        <v>76.400000000000006</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="34" t="s">
         <v>23</v>
       </c>
@@ -1073,8 +1080,9 @@
       <c r="I6" s="38"/>
       <c r="J6" s="38"/>
       <c r="K6" s="38"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L6" s="38"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="19" t="s">
         <v>24</v>
       </c>
@@ -1108,8 +1116,11 @@
       <c r="K7" s="38">
         <v>84.732329223185104</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L7" s="38">
+        <v>85.9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
         <v>25</v>
       </c>
@@ -1143,8 +1154,11 @@
       <c r="K8" s="38">
         <v>66.628666020113997</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L8" s="38">
+        <v>69.3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="25" t="s">
         <v>105</v>
       </c>
@@ -1162,8 +1176,9 @@
       <c r="I9" s="38"/>
       <c r="J9" s="38"/>
       <c r="K9" s="38"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L9" s="38"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>26</v>
       </c>
@@ -1197,8 +1212,11 @@
       <c r="K10" s="38">
         <v>72.783677442666146</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L10" s="38">
+        <v>75.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>27</v>
       </c>
@@ -1232,8 +1250,11 @@
       <c r="K11" s="38">
         <v>73.603979547335769</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L11" s="38">
+        <v>77.099999999999994</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="24" t="s">
         <v>81</v>
       </c>
@@ -1251,8 +1272,9 @@
       <c r="I12" s="38"/>
       <c r="J12" s="38"/>
       <c r="K12" s="38"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L12" s="38"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
         <v>53</v>
       </c>
@@ -1286,8 +1308,11 @@
       <c r="K13" s="38">
         <v>53.190169650876342</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L13" s="38">
+        <v>58.3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="19" t="s">
         <v>56</v>
       </c>
@@ -1321,8 +1346,11 @@
       <c r="K14" s="38">
         <v>53.980425341193509</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L14" s="38">
+        <v>54.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
         <v>58</v>
       </c>
@@ -1356,8 +1384,11 @@
       <c r="K15" s="38">
         <v>53.137495385924751</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L15" s="38">
+        <v>66.3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
         <v>60</v>
       </c>
@@ -1391,8 +1422,11 @@
       <c r="K16" s="38">
         <v>72.873094526683218</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L16" s="38">
+        <v>77.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="19" t="s">
         <v>63</v>
       </c>
@@ -1426,8 +1460,11 @@
       <c r="K17" s="38">
         <v>85.786816943292436</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L17" s="38">
+        <v>93.2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="19" t="s">
         <v>66</v>
       </c>
@@ -1461,8 +1498,11 @@
       <c r="K18" s="38">
         <v>51.070121416862371</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L18" s="38">
+        <v>47.7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
         <v>69</v>
       </c>
@@ -1496,8 +1536,11 @@
       <c r="K19" s="38">
         <v>74.345691705122476</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L19" s="38">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="19" t="s">
         <v>72</v>
       </c>
@@ -1531,8 +1574,11 @@
       <c r="K20" s="38">
         <v>95.320355478300954</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L20" s="38">
+        <v>95.7</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
         <v>75</v>
       </c>
@@ -1566,8 +1612,11 @@
       <c r="K21" s="38">
         <v>99.411762689042433</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L21" s="38">
+        <v>99.4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="25" t="s">
         <v>107</v>
       </c>
@@ -1585,8 +1634,9 @@
       <c r="I22" s="38"/>
       <c r="J22" s="38"/>
       <c r="K22" s="38"/>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L22" s="38"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="19" t="s">
         <v>28</v>
       </c>
@@ -1620,8 +1670,11 @@
       <c r="K23" s="38">
         <v>72.729359607564902</v>
       </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L23" s="38">
+        <v>75.2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="19" t="s">
         <v>29</v>
       </c>
@@ -1655,8 +1708,11 @@
       <c r="K24" s="38">
         <v>71.960490863505655</v>
       </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L24" s="38">
+        <v>75.099999999999994</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="19" t="s">
         <v>30</v>
       </c>
@@ -1690,8 +1746,11 @@
       <c r="K25" s="38">
         <v>72.296589678916334</v>
       </c>
-    </row>
-    <row r="26" spans="1:11" ht="24" x14ac:dyDescent="0.25">
+      <c r="L25" s="38">
+        <v>77.400000000000006</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A26" s="21" t="s">
         <v>102</v>
       </c>
@@ -1725,8 +1784,11 @@
       <c r="K26" s="38">
         <v>74.209057592343228</v>
       </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L26" s="38">
+        <v>76.900000000000006</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="22" t="s">
         <v>103</v>
       </c>
@@ -1760,8 +1822,11 @@
       <c r="K27" s="38">
         <v>74.103596638678965</v>
       </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L27" s="38">
+        <v>76.7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="25" t="s">
         <v>108</v>
       </c>
@@ -1779,8 +1844,9 @@
       <c r="I28" s="38"/>
       <c r="J28" s="38"/>
       <c r="K28" s="38"/>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L28" s="38"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="19" t="s">
         <v>31</v>
       </c>
@@ -1814,8 +1880,11 @@
       <c r="K29" s="38">
         <v>71.491699752852526</v>
       </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L29" s="38">
+        <v>75.2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="19" t="s">
         <v>32</v>
       </c>
@@ -1849,8 +1918,11 @@
       <c r="K30" s="38">
         <v>76.344653876851936</v>
       </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L30" s="38">
+        <v>79.900000000000006</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="23" t="s">
         <v>33</v>
       </c>
@@ -1884,8 +1956,11 @@
       <c r="K31" s="38">
         <v>69.783559341120238</v>
       </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L31" s="38">
+        <v>74.099999999999994</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="23" t="s">
         <v>34</v>
       </c>
@@ -1919,8 +1994,11 @@
       <c r="K32" s="38">
         <v>75.182624551158781</v>
       </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L32" s="38">
+        <v>76.099999999999994</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="23" t="s">
         <v>35</v>
       </c>
@@ -1954,8 +2032,11 @@
       <c r="K33" s="38">
         <v>81.728384968235133</v>
       </c>
-    </row>
-    <row r="34" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="L33" s="38">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="32" t="s">
         <v>101</v>
       </c>
@@ -1973,8 +2054,9 @@
       <c r="I34" s="38"/>
       <c r="J34" s="38"/>
       <c r="K34" s="38"/>
-    </row>
-    <row r="35" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="L34" s="38"/>
+    </row>
+    <row r="35" spans="1:12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="28" t="s">
         <v>90</v>
       </c>
@@ -2008,8 +2090,11 @@
       <c r="K35" s="38">
         <v>71.813553107833584</v>
       </c>
-    </row>
-    <row r="36" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="L35" s="38">
+        <v>79.2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="28" t="s">
         <v>91</v>
       </c>
@@ -2043,8 +2128,11 @@
       <c r="K36" s="38">
         <v>74.725444681281274</v>
       </c>
-    </row>
-    <row r="37" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="L36" s="38">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="28" t="s">
         <v>92</v>
       </c>
@@ -2078,8 +2166,11 @@
       <c r="K37" s="38">
         <v>72.409661097349684</v>
       </c>
-    </row>
-    <row r="38" spans="1:11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="L37" s="38">
+        <v>75.400000000000006</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="28" t="s">
         <v>93</v>
       </c>
@@ -2113,8 +2204,11 @@
       <c r="K38" s="38">
         <v>72.514384944125325</v>
       </c>
-    </row>
-    <row r="39" spans="1:11" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L38" s="38">
+        <v>73.5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="30" t="s">
         <v>94</v>
       </c>
@@ -2148,8 +2242,11 @@
       <c r="K39" s="7">
         <v>74.605385456584258</v>
       </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L39" s="7">
+        <v>76.8</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="5"/>
       <c r="B40" s="5"/>
       <c r="C40" s="5"/>
@@ -2162,7 +2259,7 @@
       <c r="J40" s="5"/>
       <c r="K40" s="5"/>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="5"/>
       <c r="B41" s="5"/>
       <c r="C41" s="5"/>
@@ -2175,7 +2272,7 @@
       <c r="J41" s="5"/>
       <c r="K41" s="5"/>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" s="5"/>
       <c r="B42" s="5"/>
       <c r="C42" s="5"/>
@@ -2188,7 +2285,7 @@
       <c r="J42" s="5"/>
       <c r="K42" s="5"/>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="5"/>
       <c r="B43" s="5"/>
       <c r="C43" s="5"/>
@@ -2201,7 +2298,7 @@
       <c r="J43" s="5"/>
       <c r="K43" s="5"/>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" s="5"/>
       <c r="B44" s="5"/>
       <c r="C44" s="5"/>
@@ -2214,7 +2311,7 @@
       <c r="J44" s="5"/>
       <c r="K44" s="5"/>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" s="5"/>
       <c r="B45" s="5"/>
       <c r="C45" s="5"/>
@@ -2227,7 +2324,7 @@
       <c r="J45" s="5"/>
       <c r="K45" s="5"/>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" s="5"/>
       <c r="B46" s="5"/>
       <c r="C46" s="5"/>
@@ -2240,7 +2337,7 @@
       <c r="J46" s="5"/>
       <c r="K46" s="5"/>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" s="5"/>
       <c r="B47" s="5"/>
       <c r="C47" s="5"/>
@@ -2253,7 +2350,7 @@
       <c r="J47" s="5"/>
       <c r="K47" s="5"/>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" s="5"/>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
